--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.22539348431154</v>
+        <v>11.57412644120063</v>
       </c>
       <c r="D2" t="n">
-        <v>72.36370256108805</v>
+        <v>11.75910166617681</v>
       </c>
       <c r="E2" t="n">
-        <v>0.502070106076431</v>
+        <v>0.08158639223742004</v>
       </c>
       <c r="F2" t="n">
-        <v>8.300015994869906</v>
+        <v>1.348752599166359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.2295336964644</v>
+        <v>11.73729922567547</v>
       </c>
       <c r="D3" t="n">
-        <v>55.76367057134824</v>
+        <v>9.061596467844089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.502070106076431</v>
+        <v>0.08158639223742004</v>
       </c>
       <c r="F3" t="n">
-        <v>8.300015994869906</v>
+        <v>1.348752599166359</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
